--- a/public/templates/order-import-template.xlsx
+++ b/public/templates/order-import-template.xlsx
@@ -440,7 +440,7 @@
         <v>อาการลูกค้า</v>
       </c>
       <c r="N1" t="str">
-        <v>ลูกค้ามาจาก</v>
+        <v>ช่องทางการขาย</v>
       </c>
       <c r="O1" t="str">
         <v>หมายเหตุ</v>

--- a/public/templates/order-import-template.xlsx
+++ b/public/templates/order-import-template.xlsx
@@ -425,7 +425,7 @@
         <v>ที่อยู่จัดส่ง</v>
       </c>
       <c r="I1" t="str">
-        <v>จำนวนกระปุก</v>
+        <v>จำนวน</v>
       </c>
       <c r="J1" t="str">
         <v>ยอดซื้อ</v>
